--- a/Information-Storage-Medium-Types.xlsx
+++ b/Information-Storage-Medium-Types.xlsx
@@ -3438,7 +3438,7 @@
         <v>18</v>
       </c>
       <c r="B8" s="12" t="n">
-        <v>46183</v>
+        <v>46190</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
